--- a/Starbucks_Hub_CMS.xlsx
+++ b/Starbucks_Hub_CMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1108E83-0A84-431F-8651-45CBA36FF2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E27557-67C3-40CB-A390-EA6FA6DF377A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informativo" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="410">
   <si>
     <t>Categoria</t>
   </si>
@@ -1326,6 +1326,15 @@
   </si>
   <si>
     <t>Valida Avance de Cada Taza Cuenta</t>
+  </si>
+  <si>
+    <t>https://sbx-mex.github.io/Sistemas_Evidencias_Ops/</t>
+  </si>
+  <si>
+    <t>Portal Bienestar</t>
+  </si>
+  <si>
+    <t>https://portalmasbienestar.com/#/</t>
   </si>
 </sst>
 </file>
@@ -2693,6 +2702,9 @@
       <c r="F19" s="20" t="s">
         <v>15</v>
       </c>
+      <c r="G19" t="s">
+        <v>407</v>
+      </c>
       <c r="H19" t="s">
         <v>403</v>
       </c>
@@ -2739,10 +2751,11 @@
   <hyperlinks>
     <hyperlink ref="G8" r:id="rId1" xr:uid="{BDBACA53-3662-4139-97DC-A37B8397BD29}"/>
     <hyperlink ref="G20" r:id="rId2" xr:uid="{F9F4722A-FA0C-4F47-848A-1F7B0EA247F3}"/>
+    <hyperlink ref="G19" r:id="rId3" xr:uid="{F16EA375-373B-4BE2-93F7-FDF49F5A2E8B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2752,7 +2765,7 @@
   <sheetPr>
     <tabColor rgb="FF006241"/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3358,6 +3371,17 @@
         <v>201</v>
       </c>
       <c r="D49" s="7"/>
+    </row>
+    <row r="50" spans="1:4" ht="15.5">
+      <c r="A50" s="23">
+        <v>49</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>409</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D49" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/Starbucks_Hub_CMS.xlsx
+++ b/Starbucks_Hub_CMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E27557-67C3-40CB-A390-EA6FA6DF377A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1108E83-0A84-431F-8651-45CBA36FF2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informativo" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="407">
   <si>
     <t>Categoria</t>
   </si>
@@ -1326,15 +1326,6 @@
   </si>
   <si>
     <t>Valida Avance de Cada Taza Cuenta</t>
-  </si>
-  <si>
-    <t>https://sbx-mex.github.io/Sistemas_Evidencias_Ops/</t>
-  </si>
-  <si>
-    <t>Portal Bienestar</t>
-  </si>
-  <si>
-    <t>https://portalmasbienestar.com/#/</t>
   </si>
 </sst>
 </file>
@@ -2702,9 +2693,6 @@
       <c r="F19" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G19" t="s">
-        <v>407</v>
-      </c>
       <c r="H19" t="s">
         <v>403</v>
       </c>
@@ -2751,11 +2739,10 @@
   <hyperlinks>
     <hyperlink ref="G8" r:id="rId1" xr:uid="{BDBACA53-3662-4139-97DC-A37B8397BD29}"/>
     <hyperlink ref="G20" r:id="rId2" xr:uid="{F9F4722A-FA0C-4F47-848A-1F7B0EA247F3}"/>
-    <hyperlink ref="G19" r:id="rId3" xr:uid="{F16EA375-373B-4BE2-93F7-FDF49F5A2E8B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2765,7 +2752,7 @@
   <sheetPr>
     <tabColor rgb="FF006241"/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3371,17 +3358,6 @@
         <v>201</v>
       </c>
       <c r="D49" s="7"/>
-    </row>
-    <row r="50" spans="1:4" ht="15.5">
-      <c r="A50" s="23">
-        <v>49</v>
-      </c>
-      <c r="B50" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>409</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D49" xr:uid="{00000000-0009-0000-0000-000003000000}"/>

--- a/Starbucks_Hub_CMS.xlsx
+++ b/Starbucks_Hub_CMS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecesar\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1108E83-0A84-431F-8651-45CBA36FF2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F761EA48-1EBB-4BDA-87BB-18056C5E5D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informativo" sheetId="1" r:id="rId1"/>
@@ -89,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="410">
   <si>
     <t>Categoria</t>
   </si>
@@ -1326,6 +1326,15 @@
   </si>
   <si>
     <t>Valida Avance de Cada Taza Cuenta</t>
+  </si>
+  <si>
+    <t>https://sbx-mex.github.io/Sistemas_Evidencias_Ops/</t>
+  </si>
+  <si>
+    <t>Portal Bienestar</t>
+  </si>
+  <si>
+    <t>https://portalmasbienestar.com/#/</t>
   </si>
 </sst>
 </file>
@@ -2682,7 +2691,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>401</v>
@@ -2692,6 +2701,9 @@
       </c>
       <c r="F19" s="20" t="s">
         <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>407</v>
       </c>
       <c r="H19" t="s">
         <v>403</v>
@@ -2752,7 +2764,7 @@
   <sheetPr>
     <tabColor rgb="FF006241"/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -3358,6 +3370,17 @@
         <v>201</v>
       </c>
       <c r="D49" s="7"/>
+    </row>
+    <row r="50" spans="1:4" ht="15.5">
+      <c r="A50" s="23">
+        <v>49</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>409</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D49" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
